--- a/MEME_OUTPUT/direct_meme_out_2_motif5.xlsx
+++ b/MEME_OUTPUT/direct_meme_out_2_motif5.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6296</v>
+        <v>0.6295481807277089</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.999</v>
+        <v>0.9988004798080767</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="5">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="6">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.999</v>
+        <v>0.9988004798080767</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.999</v>
+        <v>0.9988004798080767</v>
       </c>
     </row>
     <row r="8">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="9">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="10">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.999</v>
+        <v>0.9988004798080767</v>
       </c>
     </row>
     <row r="11">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.999</v>
+        <v>0.9988004798080767</v>
       </c>
     </row>
     <row r="12">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.999</v>
+        <v>0.9988004798080767</v>
       </c>
     </row>
   </sheetData>

--- a/MEME_OUTPUT/direct_meme_out_2_motif5.xlsx
+++ b/MEME_OUTPUT/direct_meme_out_2_motif5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>CGCATTAGTCACGC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>CGC</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>CGC</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;ATTAGTCA&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.6295481807277089</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>GCTCGC</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;TC&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.9988004798080767</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>TCGCATTAGTC</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;GCATTAG&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>CATTAGTCA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;TTAGT&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>GCTCGCATTAGTCACGC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;TCGCATTAGTCAC&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9988004798080767</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>CGCATTAGTCACGCG</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;CATTAGTCACG&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9988004798080767</v>
       </c>
     </row>
@@ -651,15 +721,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>CGCG</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -680,15 +760,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>AGTCACGCGAG</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;TCACGCG&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -709,15 +799,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>GCTCGCATTAGTCACGCGAGC</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;TCGCATTAGTCACGCGA&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9988004798080767</v>
       </c>
     </row>
@@ -738,15 +838,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>GCATTAGTCACGCGAGC</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;ATTAGTCACGCGA&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.9988004798080767</v>
       </c>
     </row>
@@ -767,15 +877,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>GCGAGC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;GA&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.9988004798080767</v>
       </c>
     </row>
